--- a/tata_whatsapp_50_templates.xlsx
+++ b/tata_whatsapp_50_templates.xlsx
@@ -122,6 +122,386 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1524000" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1524000" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1524000" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1524000" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1524000" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1524000" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1524000" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1524000" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1524000" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1524000" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1524000" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1524000" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1524000" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1524000" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1524000" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -413,10 +793,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K51"/>
+  <dimension ref="A1:L51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="32" customWidth="1" min="12" max="12"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" t="inlineStr">
         <is>
           <t>template_name</t>
@@ -472,8 +866,13 @@
           <t>button_url_example</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>sample_creative_preview</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="76" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
           <t>tata_testing_1</t>
@@ -525,8 +924,9 @@
           <t>https://www.tatacapital.com/apply/12345</t>
         </is>
       </c>
-    </row>
-    <row r="3">
+      <c r="L2" t="inlineStr"/>
+    </row>
+    <row r="3" ht="76" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
           <t>tata_testing_2</t>
@@ -578,8 +978,9 @@
           <t>https://www.tatacapital.com/home-loan</t>
         </is>
       </c>
-    </row>
-    <row r="4">
+      <c r="L3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="76" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
           <t>tata_testing_3</t>
@@ -623,8 +1024,9 @@
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-    </row>
-    <row r="5">
+      <c r="L4" t="inlineStr"/>
+    </row>
+    <row r="5" ht="76" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
           <t>tata_testing_4</t>
@@ -676,8 +1078,9 @@
           <t>https://www.tatacapital.com/business-loan</t>
         </is>
       </c>
-    </row>
-    <row r="6">
+      <c r="L5" t="inlineStr"/>
+    </row>
+    <row r="6" ht="76" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
           <t>tata_testing_5</t>
@@ -729,8 +1132,9 @@
           <t>https://www.tatacapital.com/gold-loan</t>
         </is>
       </c>
-    </row>
-    <row r="7">
+      <c r="L6" t="inlineStr"/>
+    </row>
+    <row r="7" ht="76" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
           <t>tata_testing_6</t>
@@ -782,8 +1186,9 @@
           <t>https://www.tatacapital.com/festive-offer</t>
         </is>
       </c>
-    </row>
-    <row r="8">
+      <c r="L7" t="inlineStr"/>
+    </row>
+    <row r="8" ht="76" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
           <t>tata_testing_7</t>
@@ -835,8 +1240,9 @@
           <t>https://www.tatacapital.com/app</t>
         </is>
       </c>
-    </row>
-    <row r="9">
+      <c r="L8" t="inlineStr"/>
+    </row>
+    <row r="9" ht="76" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
           <t>tata_testing_8</t>
@@ -880,8 +1286,9 @@
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-    </row>
-    <row r="10">
+      <c r="L9" t="inlineStr"/>
+    </row>
+    <row r="10" ht="76" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
           <t>tata_testing_9</t>
@@ -933,8 +1340,9 @@
           <t>https://www.tatacapital.com/doctor-loan</t>
         </is>
       </c>
-    </row>
-    <row r="11">
+      <c r="L10" t="inlineStr"/>
+    </row>
+    <row r="11" ht="76" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
           <t>tata_testing_10</t>
@@ -986,8 +1394,9 @@
           <t>https://www.tatacapital.com/insurance</t>
         </is>
       </c>
-    </row>
-    <row r="12">
+      <c r="L11" t="inlineStr"/>
+    </row>
+    <row r="12" ht="76" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
           <t>tata_testing_11</t>
@@ -1039,8 +1448,9 @@
           <t>https://www.tatacapital.com/card</t>
         </is>
       </c>
-    </row>
-    <row r="13">
+      <c r="L12" t="inlineStr"/>
+    </row>
+    <row r="13" ht="76" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
           <t>tata_testing_12</t>
@@ -1084,8 +1494,9 @@
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-    </row>
-    <row r="14">
+      <c r="L13" t="inlineStr"/>
+    </row>
+    <row r="14" ht="76" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
           <t>tata_testing_13</t>
@@ -1137,8 +1548,9 @@
           <t>https://www.tatacapital.com/hindi</t>
         </is>
       </c>
-    </row>
-    <row r="15">
+      <c r="L14" t="inlineStr"/>
+    </row>
+    <row r="15" ht="76" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
           <t>tata_testing_14</t>
@@ -1190,8 +1602,9 @@
           <t>https://www.tatacapital.com/travel</t>
         </is>
       </c>
-    </row>
-    <row r="16">
+      <c r="L15" t="inlineStr"/>
+    </row>
+    <row r="16" ht="76" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
           <t>tata_testing_15</t>
@@ -1243,8 +1656,9 @@
           <t>https://www.tatacapital.com/fd</t>
         </is>
       </c>
-    </row>
-    <row r="17">
+      <c r="L16" t="inlineStr"/>
+    </row>
+    <row r="17" ht="24" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
           <t>tata_testing_16</t>
@@ -1296,8 +1710,9 @@
           <t>https://www.tatacapital.com/video-demo</t>
         </is>
       </c>
-    </row>
-    <row r="18">
+      <c r="L17" t="inlineStr"/>
+    </row>
+    <row r="18" ht="24" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
           <t>tata_testing_17</t>
@@ -1341,8 +1756,9 @@
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-    </row>
-    <row r="19">
+      <c r="L18" t="inlineStr"/>
+    </row>
+    <row r="19" ht="24" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
           <t>tata_testing_18</t>
@@ -1394,8 +1810,9 @@
           <t>https://www.tatacapital.com/emandate</t>
         </is>
       </c>
-    </row>
-    <row r="20">
+      <c r="L19" t="inlineStr"/>
+    </row>
+    <row r="20" ht="24" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
           <t>tata_testing_19</t>
@@ -1447,8 +1864,9 @@
           <t>https://www.tatacapital.com/solar</t>
         </is>
       </c>
-    </row>
-    <row r="21">
+      <c r="L20" t="inlineStr"/>
+    </row>
+    <row r="21" ht="24" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
           <t>tata_testing_20</t>
@@ -1500,8 +1918,9 @@
           <t>https://www.tatacapital.com/cibil</t>
         </is>
       </c>
-    </row>
-    <row r="22">
+      <c r="L21" t="inlineStr"/>
+    </row>
+    <row r="22" ht="24" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
           <t>tata_testing_21</t>
@@ -1545,8 +1964,9 @@
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-    </row>
-    <row r="23">
+      <c r="L22" t="inlineStr"/>
+    </row>
+    <row r="23" ht="24" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
           <t>tata_testing_22</t>
@@ -1598,8 +2018,9 @@
           <t>https://www.tatacapital.com/app-video</t>
         </is>
       </c>
-    </row>
-    <row r="24">
+      <c r="L23" t="inlineStr"/>
+    </row>
+    <row r="24" ht="24" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
           <t>tata_testing_23</t>
@@ -1643,8 +2064,9 @@
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-    </row>
-    <row r="25">
+      <c r="L24" t="inlineStr"/>
+    </row>
+    <row r="25" ht="24" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
           <t>tata_testing_24</t>
@@ -1696,8 +2118,9 @@
           <t>https://www.tatacapital.com/sanction</t>
         </is>
       </c>
-    </row>
-    <row r="26">
+      <c r="L25" t="inlineStr"/>
+    </row>
+    <row r="26" ht="24" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
           <t>tata_testing_25</t>
@@ -1741,8 +2164,9 @@
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-    </row>
-    <row r="27">
+      <c r="L26" t="inlineStr"/>
+    </row>
+    <row r="27" ht="24" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
           <t>tata_testing_26</t>
@@ -1794,8 +2218,9 @@
           <t>https://www.tatacapital.com/schedule</t>
         </is>
       </c>
-    </row>
-    <row r="28">
+      <c r="L27" t="inlineStr"/>
+    </row>
+    <row r="28" ht="24" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
           <t>tata_testing_27</t>
@@ -1839,8 +2264,9 @@
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-    </row>
-    <row r="29">
+      <c r="L28" t="inlineStr"/>
+    </row>
+    <row r="29" ht="24" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
           <t>tata_testing_28</t>
@@ -1884,8 +2310,9 @@
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-    </row>
-    <row r="30">
+      <c r="L29" t="inlineStr"/>
+    </row>
+    <row r="30" ht="24" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
           <t>tata_testing_29</t>
@@ -1941,8 +2368,9 @@
           <t>https://www.tatacapital.com/preapproved</t>
         </is>
       </c>
-    </row>
-    <row r="31">
+      <c r="L30" t="inlineStr"/>
+    </row>
+    <row r="31" ht="24" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
           <t>tata_testing_30</t>
@@ -1998,8 +2426,9 @@
           <t>https://www.tatacapital.com/two-wheeler</t>
         </is>
       </c>
-    </row>
-    <row r="32">
+      <c r="L31" t="inlineStr"/>
+    </row>
+    <row r="32" ht="24" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
           <t>tata_testing_31</t>
@@ -2047,8 +2476,9 @@
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-    </row>
-    <row r="33">
+      <c r="L32" t="inlineStr"/>
+    </row>
+    <row r="33" ht="24" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
           <t>tata_testing_32</t>
@@ -2104,8 +2534,9 @@
           <t>https://www.tatacapital.com/sme</t>
         </is>
       </c>
-    </row>
-    <row r="34">
+      <c r="L33" t="inlineStr"/>
+    </row>
+    <row r="34" ht="24" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
           <t>tata_testing_33</t>
@@ -2161,8 +2592,9 @@
           <t>https://www.tatacapital.com/renovate</t>
         </is>
       </c>
-    </row>
-    <row r="35">
+      <c r="L34" t="inlineStr"/>
+    </row>
+    <row r="35" ht="24" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
           <t>tata_testing_34</t>
@@ -2218,8 +2650,9 @@
           <t>https://www.tatacapital.com/hi-loan</t>
         </is>
       </c>
-    </row>
-    <row r="36">
+      <c r="L35" t="inlineStr"/>
+    </row>
+    <row r="36" ht="24" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
           <t>tata_testing_35</t>
@@ -2267,8 +2700,9 @@
       </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-    </row>
-    <row r="37">
+      <c r="L36" t="inlineStr"/>
+    </row>
+    <row r="37" ht="24" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
           <t>tata_testing_36</t>
@@ -2324,8 +2758,9 @@
           <t>https://www.tatacapital.com/used-car</t>
         </is>
       </c>
-    </row>
-    <row r="38">
+      <c r="L37" t="inlineStr"/>
+    </row>
+    <row r="38" ht="24" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
           <t>tata_testing_37</t>
@@ -2369,8 +2804,9 @@
       </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-    </row>
-    <row r="39">
+      <c r="L38" t="inlineStr"/>
+    </row>
+    <row r="39" ht="24" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
           <t>tata_testing_38</t>
@@ -2410,8 +2846,9 @@
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-    </row>
-    <row r="40">
+      <c r="L39" t="inlineStr"/>
+    </row>
+    <row r="40" ht="24" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
           <t>tata_testing_39</t>
@@ -2463,8 +2900,9 @@
           <t>https://www.tatacapital.com/instant</t>
         </is>
       </c>
-    </row>
-    <row r="41">
+      <c r="L40" t="inlineStr"/>
+    </row>
+    <row r="41" ht="24" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
           <t>tata_testing_40</t>
@@ -2516,8 +2954,9 @@
           <t>https://www.tatacapital.com/refer</t>
         </is>
       </c>
-    </row>
-    <row r="42">
+      <c r="L41" t="inlineStr"/>
+    </row>
+    <row r="42" ht="24" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
           <t>tata_testing_41</t>
@@ -2569,8 +3008,9 @@
           <t>https://www.tatacapital.com/credit-score</t>
         </is>
       </c>
-    </row>
-    <row r="43">
+      <c r="L42" t="inlineStr"/>
+    </row>
+    <row r="43" ht="24" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
           <t>tata_testing_42</t>
@@ -2622,8 +3062,9 @@
           <t>https://www.tatacapital.com/business-hi</t>
         </is>
       </c>
-    </row>
-    <row r="44">
+      <c r="L43" t="inlineStr"/>
+    </row>
+    <row r="44" ht="24" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
           <t>tata_testing_43</t>
@@ -2667,8 +3108,9 @@
       </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-    </row>
-    <row r="45">
+      <c r="L44" t="inlineStr"/>
+    </row>
+    <row r="45" ht="24" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
           <t>tata_testing_44</t>
@@ -2720,8 +3162,9 @@
           <t>https://www.tatacapital.com/women-loan</t>
         </is>
       </c>
-    </row>
-    <row r="46">
+      <c r="L45" t="inlineStr"/>
+    </row>
+    <row r="46" ht="24" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
           <t>tata_testing_45</t>
@@ -2777,8 +3220,9 @@
           <t>https://www.tatacapital.com/pay</t>
         </is>
       </c>
-    </row>
-    <row r="47">
+      <c r="L46" t="inlineStr"/>
+    </row>
+    <row r="47" ht="24" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
           <t>tata_testing_46</t>
@@ -2826,8 +3270,9 @@
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-    </row>
-    <row r="48">
+      <c r="L47" t="inlineStr"/>
+    </row>
+    <row r="48" ht="24" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
           <t>tata_testing_47</t>
@@ -2867,8 +3312,9 @@
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-    </row>
-    <row r="49">
+      <c r="L48" t="inlineStr"/>
+    </row>
+    <row r="49" ht="24" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
           <t>tata_testing_48</t>
@@ -2924,8 +3370,9 @@
           <t>https://www.tatacapital.com/disbursal</t>
         </is>
       </c>
-    </row>
-    <row r="50">
+      <c r="L49" t="inlineStr"/>
+    </row>
+    <row r="50" ht="24" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
           <t>tata_testing_49</t>
@@ -2977,8 +3424,9 @@
           <t>https://www.tatacapital.com/esign</t>
         </is>
       </c>
-    </row>
-    <row r="51">
+      <c r="L50" t="inlineStr"/>
+    </row>
+    <row r="51" ht="24" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
           <t>tata_testing_50</t>
@@ -3026,8 +3474,10 @@
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>